--- a/produtos.xlsx
+++ b/produtos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,243 +482,6 @@
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t>fornecedor</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>AL-001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>RODO CABO DE ALUMINIO</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>MATERIAIS DE LIMPEZA</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>COL-01 / RUA-01</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>rodo cabo de aluminio.webp</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>🟢 OK</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>UN</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>12.75</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>AL-002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>PERNEIRA</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>EPI'S</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>COL-02 / RUA-05</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>perneira.webp</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>8</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>🟢 OK</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>UN</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>AL-003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>LUVA NITRILICA</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>EPI'S</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>COL-01 / RUA-03</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>luva nitrilica.jpg</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>🔴 ESTOQUE BAIXO</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>UN</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>CENTRAL EPI'S</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AL-004</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>COADOR DE PANO</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>COPA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>COL-02 / RUA5</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>coador.webp</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>🟢 OK</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>UN</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>5</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>CENTRAL EPI'S</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>AL-005</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>CANECA ALPES</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>COPA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>AL-005_CANECA_ALPES.jpeg</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>UN</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>50</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>CENTRAL EPI'S</t>
         </is>
       </c>
     </row>
